--- a/esp32_pin.xlsx
+++ b/esp32_pin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DAVI2\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBE8B409-5FE1-4E32-AC72-671F60D6045A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0124F409-8232-465E-A5E1-AB516F65005C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{B70DDFC4-BD73-4640-93D6-4540E0AF298E}"/>
+    <workbookView xWindow="288" yWindow="648" windowWidth="17280" windowHeight="9960" xr2:uid="{B70DDFC4-BD73-4640-93D6-4540E0AF298E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="19">
   <si>
     <t>NUMBER</t>
   </si>
@@ -69,13 +69,28 @@
     <t>MISO</t>
   </si>
   <si>
-    <t>GPIO</t>
-  </si>
-  <si>
     <t>NO</t>
   </si>
   <si>
     <t>DOESN’T EXIST</t>
+  </si>
+  <si>
+    <t>need 2 pin changes</t>
+  </si>
+  <si>
+    <t>DON’T</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">available functions </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIN CHANGE - ENCODER </t>
+  </si>
+  <si>
+    <t>TRIGGER - ULTRASONIC</t>
   </si>
 </sst>
 </file>
@@ -427,14 +442,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5209903B-8342-44AC-9779-0A6B76C670FB}">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -444,8 +460,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -453,10 +472,10 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -464,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -475,10 +494,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -486,10 +505,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -500,7 +519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -511,7 +530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -522,18 +541,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -541,10 +557,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -555,7 +571,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -566,7 +582,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -577,7 +593,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -588,7 +604,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -596,10 +612,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -618,7 +634,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -629,7 +645,7 @@
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -640,7 +656,7 @@
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -648,7 +664,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -656,7 +672,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -675,7 +691,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -683,7 +699,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -691,7 +707,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -699,7 +715,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -707,7 +723,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -715,7 +731,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -723,7 +739,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -731,7 +747,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -739,7 +755,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -747,7 +763,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -755,7 +771,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -763,7 +779,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -771,7 +787,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -779,7 +795,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -787,7 +803,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -795,7 +811,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -803,10 +819,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -814,7 +827,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C40" t="s">
         <v>6</v>
@@ -858,7 +871,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -866,7 +879,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -874,7 +887,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -882,7 +895,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -890,21 +903,20 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>3</v>
-      </c>
-      <c r="C49" t="s">
-        <v>5</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/esp32_pin.xlsx
+++ b/esp32_pin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DAVI2\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tkqa1ex/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0124F409-8232-465E-A5E1-AB516F65005C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5029776-8C2A-E941-AED9-6C7B0C005168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="288" yWindow="648" windowWidth="17280" windowHeight="9960" xr2:uid="{B70DDFC4-BD73-4640-93D6-4540E0AF298E}"/>
+    <workbookView xWindow="280" yWindow="680" windowWidth="17280" windowHeight="9960" xr2:uid="{B70DDFC4-BD73-4640-93D6-4540E0AF298E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="21">
   <si>
     <t>NUMBER</t>
   </si>
@@ -48,15 +48,6 @@
     <t>YES</t>
   </si>
   <si>
-    <t>ADC</t>
-  </si>
-  <si>
-    <t>PIN CHANGE</t>
-  </si>
-  <si>
-    <t>PWM</t>
-  </si>
-  <si>
     <t>CS</t>
   </si>
   <si>
@@ -91,6 +82,21 @@
   </si>
   <si>
     <t>TRIGGER - ULTRASONIC</t>
+  </si>
+  <si>
+    <t>ADC - IR</t>
+  </si>
+  <si>
+    <t>PIN CHANGE - DAT pn load cell apmlifier</t>
+  </si>
+  <si>
+    <t>PIN CHANGE - Echo - Ultrasonic</t>
+  </si>
+  <si>
+    <t>PWM - clk load cell</t>
+  </si>
+  <si>
+    <t>PWM - motor driver</t>
   </si>
 </sst>
 </file>
@@ -146,9 +152,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -186,7 +192,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -292,7 +298,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -434,7 +440,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -443,14 +449,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5209903B-8342-44AC-9779-0A6B76C670FB}">
   <dimension ref="A1:D51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -461,10 +467,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -472,10 +478,10 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -483,21 +489,18 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -505,10 +508,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -516,10 +519,10 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -527,10 +530,10 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -538,18 +541,18 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -557,10 +560,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -568,10 +571,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -579,10 +582,10 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -590,10 +593,10 @@
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -601,10 +604,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -612,10 +615,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -623,10 +626,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -634,10 +637,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -645,10 +648,10 @@
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -656,26 +659,26 @@
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -683,157 +686,157 @@
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -841,10 +844,10 @@
         <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -852,10 +855,10 @@
         <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -863,60 +866,60 @@
         <v>3</v>
       </c>
       <c r="C43" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
